--- a/docs/SpriteChecklist.xlsx
+++ b/docs/SpriteChecklist.xlsx
@@ -47300,7 +47300,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Pear Emerald</t>
+          <t>Rose Emerald</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -47319,7 +47319,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Pear Sapphire</t>
+          <t>Rose Sapphire</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -47338,7 +47338,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Pear Ruby</t>
+          <t>Rose Ruby</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">

--- a/docs/SpriteChecklist.xlsx
+++ b/docs/SpriteChecklist.xlsx
@@ -47200,7 +47200,11 @@
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="7" t="inlineStr"/>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -47219,7 +47223,11 @@
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -47238,7 +47246,11 @@
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -47257,7 +47269,11 @@
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -47276,7 +47292,11 @@
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -47295,7 +47315,11 @@
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -47314,7 +47338,11 @@
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -47333,7 +47361,11 @@
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -47352,7 +47384,11 @@
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -47371,7 +47407,11 @@
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -47390,7 +47430,11 @@
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -47409,7 +47453,11 @@
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -47430,7 +47478,7 @@
       <c r="D14" s="8" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>could reuse the Crown's icon or get a grander one</t>
+          <t>placeholder in the game, drawn by tools/sprites/make_crown_icons.py; the owner's icon replaces it; could reuse the Crown's icon or get a grander one</t>
         </is>
       </c>
     </row>

--- a/docs/SpriteChecklist.xlsx
+++ b/docs/SpriteChecklist.xlsx
@@ -22544,7 +22544,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F495" s="8" t="inlineStr"/>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G495" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22584,7 +22588,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F496" s="8" t="inlineStr"/>
+      <c r="F496" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G496" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22624,7 +22632,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F497" s="8" t="inlineStr"/>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G497" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22664,7 +22676,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F498" s="8" t="inlineStr"/>
+      <c r="F498" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G498" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22704,7 +22720,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F499" s="8" t="inlineStr"/>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G499" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22744,7 +22764,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F500" s="8" t="inlineStr"/>
+      <c r="F500" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G500" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22784,7 +22808,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F501" s="8" t="inlineStr"/>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G501" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22824,7 +22852,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F502" s="8" t="inlineStr"/>
+      <c r="F502" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G502" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22864,7 +22896,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F503" s="8" t="inlineStr"/>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G503" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22904,7 +22940,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F504" s="8" t="inlineStr"/>
+      <c r="F504" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G504" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22944,7 +22984,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F505" s="8" t="inlineStr"/>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G505" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22984,7 +23028,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F506" s="8" t="inlineStr"/>
+      <c r="F506" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G506" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23024,7 +23072,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F507" s="8" t="inlineStr"/>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G507" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23064,7 +23116,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F508" s="8" t="inlineStr"/>
+      <c r="F508" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G508" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23104,7 +23160,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F509" s="8" t="inlineStr"/>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G509" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23144,7 +23204,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F510" s="8" t="inlineStr"/>
+      <c r="F510" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G510" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23184,7 +23248,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F511" s="8" t="inlineStr"/>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G511" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23224,7 +23292,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F512" s="8" t="inlineStr"/>
+      <c r="F512" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G512" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23264,7 +23336,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F513" s="8" t="inlineStr"/>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G513" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23304,7 +23380,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F514" s="8" t="inlineStr"/>
+      <c r="F514" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23344,7 +23424,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F515" s="8" t="inlineStr"/>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G515" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23384,7 +23468,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F516" s="8" t="inlineStr"/>
+      <c r="F516" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G516" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23424,7 +23512,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F517" s="8" t="inlineStr"/>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G517" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23464,7 +23556,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F518" s="8" t="inlineStr"/>
+      <c r="F518" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23504,7 +23600,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F519" s="8" t="inlineStr"/>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G519" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23544,7 +23644,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F520" s="8" t="inlineStr"/>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G520" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23584,7 +23688,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F521" s="8" t="inlineStr"/>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G521" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23624,7 +23732,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F522" s="8" t="inlineStr"/>
+      <c r="F522" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G522" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23664,7 +23776,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F523" s="8" t="inlineStr"/>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G523" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23704,7 +23820,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F524" s="8" t="inlineStr"/>
+      <c r="F524" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G524" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23744,7 +23864,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F525" s="8" t="inlineStr"/>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G525" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23784,7 +23908,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F526" s="8" t="inlineStr"/>
+      <c r="F526" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G526" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23824,7 +23952,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F527" s="8" t="inlineStr"/>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G527" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23864,7 +23996,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F528" s="8" t="inlineStr"/>
+      <c r="F528" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G528" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23904,7 +24040,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F529" s="8" t="inlineStr"/>
+      <c r="F529" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G529" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23944,7 +24084,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F530" s="8" t="inlineStr"/>
+      <c r="F530" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G530" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23984,7 +24128,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F531" s="8" t="inlineStr"/>
+      <c r="F531" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24024,7 +24172,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F532" s="8" t="inlineStr"/>
+      <c r="F532" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G532" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24064,7 +24216,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F533" s="8" t="inlineStr"/>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G533" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24104,7 +24260,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F534" s="8" t="inlineStr"/>
+      <c r="F534" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G534" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24144,7 +24304,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F535" s="8" t="inlineStr"/>
+      <c r="F535" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24184,7 +24348,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F536" s="8" t="inlineStr"/>
+      <c r="F536" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G536" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24224,7 +24392,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F537" s="8" t="inlineStr"/>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G537" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24264,7 +24436,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F538" s="8" t="inlineStr"/>
+      <c r="F538" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G538" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24304,7 +24480,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F539" s="8" t="inlineStr"/>
+      <c r="F539" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G539" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24344,7 +24524,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F540" s="8" t="inlineStr"/>
+      <c r="F540" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G540" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24384,7 +24568,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F541" s="8" t="inlineStr"/>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G541" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24424,7 +24612,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F542" s="8" t="inlineStr"/>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G542" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24464,7 +24656,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F543" s="8" t="inlineStr"/>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G543" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24504,7 +24700,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F544" s="8" t="inlineStr"/>
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G544" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24544,7 +24744,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F545" s="8" t="inlineStr"/>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24584,7 +24788,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F546" s="8" t="inlineStr"/>
+      <c r="F546" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G546" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24624,7 +24832,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F547" s="8" t="inlineStr"/>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G547" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24664,7 +24876,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F548" s="8" t="inlineStr"/>
+      <c r="F548" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G548" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24704,7 +24920,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F549" s="8" t="inlineStr"/>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G549" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24744,7 +24964,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F550" s="8" t="inlineStr"/>
+      <c r="F550" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G550" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24784,7 +25008,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F551" s="8" t="inlineStr"/>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G551" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24824,7 +25052,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F552" s="8" t="inlineStr"/>
+      <c r="F552" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G552" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24864,7 +25096,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F553" s="8" t="inlineStr"/>
+      <c r="F553" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24904,7 +25140,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F554" s="8" t="inlineStr"/>
+      <c r="F554" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G554" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24944,7 +25184,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F555" s="8" t="inlineStr"/>
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G555" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24984,7 +25228,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F556" s="8" t="inlineStr"/>
+      <c r="F556" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G556" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25024,7 +25272,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F557" s="8" t="inlineStr"/>
+      <c r="F557" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25064,7 +25316,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F558" s="8" t="inlineStr"/>
+      <c r="F558" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G558" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25104,7 +25360,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F559" s="8" t="inlineStr"/>
+      <c r="F559" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G559" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25144,7 +25404,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F560" s="8" t="inlineStr"/>
+      <c r="F560" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G560" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25184,7 +25448,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F561" s="8" t="inlineStr"/>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G561" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25224,7 +25492,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F562" s="8" t="inlineStr"/>
+      <c r="F562" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G562" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25264,7 +25536,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F563" s="8" t="inlineStr"/>
+      <c r="F563" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25304,7 +25580,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F564" s="8" t="inlineStr"/>
+      <c r="F564" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25344,7 +25624,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F565" s="8" t="inlineStr"/>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G565" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25384,7 +25668,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F566" s="8" t="inlineStr"/>
+      <c r="F566" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G566" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25424,7 +25712,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F567" s="8" t="inlineStr"/>
+      <c r="F567" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25464,7 +25756,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F568" s="8" t="inlineStr"/>
+      <c r="F568" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G568" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25504,7 +25800,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F569" s="8" t="inlineStr"/>
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25544,7 +25844,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F570" s="8" t="inlineStr"/>
+      <c r="F570" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G570" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25584,7 +25888,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F571" s="8" t="inlineStr"/>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25624,7 +25932,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F572" s="8" t="inlineStr"/>
+      <c r="F572" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G572" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25664,7 +25976,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F573" s="8" t="inlineStr"/>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G573" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25704,7 +26020,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F574" s="8" t="inlineStr"/>
+      <c r="F574" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G574" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25744,7 +26064,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F575" s="8" t="inlineStr"/>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G575" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25784,7 +26108,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F576" s="8" t="inlineStr"/>
+      <c r="F576" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G576" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25824,7 +26152,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F577" s="8" t="inlineStr"/>
+      <c r="F577" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G577" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25864,7 +26196,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F578" s="8" t="inlineStr"/>
+      <c r="F578" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G578" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25904,7 +26240,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F579" s="8" t="inlineStr"/>
+      <c r="F579" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G579" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25944,7 +26284,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F580" s="8" t="inlineStr"/>
+      <c r="F580" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G580" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25984,7 +26328,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F581" s="8" t="inlineStr"/>
+      <c r="F581" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G581" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26024,7 +26372,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F582" s="8" t="inlineStr"/>
+      <c r="F582" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G582" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26064,7 +26416,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F583" s="8" t="inlineStr"/>
+      <c r="F583" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G583" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26104,7 +26460,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F584" s="8" t="inlineStr"/>
+      <c r="F584" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G584" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26144,7 +26504,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F585" s="8" t="inlineStr"/>
+      <c r="F585" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G585" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26184,7 +26548,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F586" s="8" t="inlineStr"/>
+      <c r="F586" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G586" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26224,7 +26592,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F587" s="8" t="inlineStr"/>
+      <c r="F587" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G587" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26264,7 +26636,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F588" s="8" t="inlineStr"/>
+      <c r="F588" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G588" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26304,7 +26680,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F589" s="8" t="inlineStr"/>
+      <c r="F589" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G589" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26344,7 +26724,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F590" s="8" t="inlineStr"/>
+      <c r="F590" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G590" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26384,7 +26768,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F591" s="8" t="inlineStr"/>
+      <c r="F591" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G591" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26424,7 +26812,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F592" s="8" t="inlineStr"/>
+      <c r="F592" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G592" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26464,7 +26856,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F593" s="8" t="inlineStr"/>
+      <c r="F593" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G593" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26504,7 +26900,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F594" s="8" t="inlineStr"/>
+      <c r="F594" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G594" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26544,7 +26944,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F595" s="8" t="inlineStr"/>
+      <c r="F595" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G595" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26584,7 +26988,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F596" s="8" t="inlineStr"/>
+      <c r="F596" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G596" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26624,7 +27032,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F597" s="8" t="inlineStr"/>
+      <c r="F597" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G597" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26664,7 +27076,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F598" s="8" t="inlineStr"/>
+      <c r="F598" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26704,7 +27120,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F599" s="8" t="inlineStr"/>
+      <c r="F599" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G599" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26744,7 +27164,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F600" s="8" t="inlineStr"/>
+      <c r="F600" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G600" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26784,7 +27208,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F601" s="8" t="inlineStr"/>
+      <c r="F601" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G601" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26824,7 +27252,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F602" s="8" t="inlineStr"/>
+      <c r="F602" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G602" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26864,7 +27296,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F603" s="8" t="inlineStr"/>
+      <c r="F603" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G603" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26904,7 +27340,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F604" s="8" t="inlineStr"/>
+      <c r="F604" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G604" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26944,7 +27384,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F605" s="8" t="inlineStr"/>
+      <c r="F605" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G605" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26984,7 +27428,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F606" s="8" t="inlineStr"/>
+      <c r="F606" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G606" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27024,7 +27472,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F607" s="8" t="inlineStr"/>
+      <c r="F607" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G607" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27064,7 +27516,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F608" s="8" t="inlineStr"/>
+      <c r="F608" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27104,7 +27560,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F609" s="8" t="inlineStr"/>
+      <c r="F609" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27144,7 +27604,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F610" s="8" t="inlineStr"/>
+      <c r="F610" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27184,7 +27648,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F611" s="8" t="inlineStr"/>
+      <c r="F611" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G611" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27224,7 +27692,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F612" s="8" t="inlineStr"/>
+      <c r="F612" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G612" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27264,7 +27736,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F613" s="8" t="inlineStr"/>
+      <c r="F613" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G613" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27304,7 +27780,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F614" s="8" t="inlineStr"/>
+      <c r="F614" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27344,7 +27824,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F615" s="8" t="inlineStr"/>
+      <c r="F615" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G615" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27384,7 +27868,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F616" s="8" t="inlineStr"/>
+      <c r="F616" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G616" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27424,7 +27912,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F617" s="8" t="inlineStr"/>
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G617" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27464,7 +27956,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F618" s="8" t="inlineStr"/>
+      <c r="F618" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G618" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27504,7 +28000,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F619" s="8" t="inlineStr"/>
+      <c r="F619" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G619" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27544,7 +28044,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F620" s="8" t="inlineStr"/>
+      <c r="F620" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G620" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27584,7 +28088,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F621" s="8" t="inlineStr"/>
+      <c r="F621" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G621" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27624,7 +28132,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F622" s="8" t="inlineStr"/>
+      <c r="F622" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G622" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27664,7 +28176,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F623" s="8" t="inlineStr"/>
+      <c r="F623" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G623" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27704,7 +28220,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F624" s="8" t="inlineStr"/>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G624" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27744,7 +28264,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F625" s="8" t="inlineStr"/>
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G625" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27784,7 +28308,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F626" s="8" t="inlineStr"/>
+      <c r="F626" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G626" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27824,7 +28352,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F627" s="8" t="inlineStr"/>
+      <c r="F627" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G627" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27864,7 +28396,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F628" s="8" t="inlineStr"/>
+      <c r="F628" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G628" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27904,7 +28440,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F629" s="8" t="inlineStr"/>
+      <c r="F629" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G629" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27944,7 +28484,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F630" s="8" t="inlineStr"/>
+      <c r="F630" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G630" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27984,7 +28528,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F631" s="8" t="inlineStr"/>
+      <c r="F631" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G631" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28024,7 +28572,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F632" s="8" t="inlineStr"/>
+      <c r="F632" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G632" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28064,7 +28616,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F633" s="8" t="inlineStr"/>
+      <c r="F633" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G633" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28104,7 +28660,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F634" s="8" t="inlineStr"/>
+      <c r="F634" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G634" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28144,7 +28704,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F635" s="8" t="inlineStr"/>
+      <c r="F635" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G635" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28184,7 +28748,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F636" s="8" t="inlineStr"/>
+      <c r="F636" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G636" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28224,7 +28792,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F637" s="8" t="inlineStr"/>
+      <c r="F637" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G637" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28264,7 +28836,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F638" s="8" t="inlineStr"/>
+      <c r="F638" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G638" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28304,7 +28880,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F639" s="8" t="inlineStr"/>
+      <c r="F639" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G639" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28344,7 +28924,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F640" s="8" t="inlineStr"/>
+      <c r="F640" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G640" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28384,7 +28968,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F641" s="8" t="inlineStr"/>
+      <c r="F641" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G641" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28424,7 +29012,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F642" s="8" t="inlineStr"/>
+      <c r="F642" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G642" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28464,7 +29056,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F643" s="8" t="inlineStr"/>
+      <c r="F643" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G643" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28504,7 +29100,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F644" s="8" t="inlineStr"/>
+      <c r="F644" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G644" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28544,7 +29144,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F645" s="8" t="inlineStr"/>
+      <c r="F645" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G645" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28584,7 +29188,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F646" s="8" t="inlineStr"/>
+      <c r="F646" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G646" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28624,7 +29232,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F647" s="8" t="inlineStr"/>
+      <c r="F647" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G647" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28664,7 +29276,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F648" s="8" t="inlineStr"/>
+      <c r="F648" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G648" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28704,7 +29320,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F649" s="8" t="inlineStr"/>
+      <c r="F649" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G649" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28744,7 +29364,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F650" s="8" t="inlineStr"/>
+      <c r="F650" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G650" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28998,7 +29622,7 @@
       </c>
       <c r="J655" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (not a clean 2x upscale)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29670,7 @@
       </c>
       <c r="J656" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 87x89); shiny front: resize/redraw (96x96, art 87x89); shiny back: resize/redraw (not a clean 2x upscale)</t>
+          <t>front: resize/redraw (96x96, art 87x89); shiny front: resize/redraw (96x96, art 87x89)</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29766,7 @@
       </c>
       <c r="J658" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (not a clean 2x upscale)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29958,7 @@
       </c>
       <c r="J662" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (16 colours)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -29552,7 +30176,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F667" s="8" t="inlineStr"/>
+      <c r="F667" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G667" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29568,11 +30196,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J667" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (29 colours)</t>
-        </is>
-      </c>
+      <c r="J667" s="7" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="7" t="n">
@@ -29692,7 +30316,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F670" s="8" t="inlineStr"/>
+      <c r="F670" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G670" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29732,7 +30360,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F671" s="8" t="inlineStr"/>
+      <c r="F671" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G671" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29748,11 +30380,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J671" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (16 colours)</t>
-        </is>
-      </c>
+      <c r="J671" s="7" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="7" t="n">
@@ -29776,7 +30404,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F672" s="8" t="inlineStr"/>
+      <c r="F672" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G672" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29792,11 +30424,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J672" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (16 colours)</t>
-        </is>
-      </c>
+      <c r="J672" s="7" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="7" t="n">
@@ -29873,7 +30501,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G674" s="8" t="inlineStr"/>
+      <c r="G674" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H674" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30008,8 +30640,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F677" s="8" t="inlineStr"/>
-      <c r="G677" s="8" t="inlineStr"/>
+      <c r="F677" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G677" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30140,7 +30780,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F680" s="8" t="inlineStr"/>
+      <c r="F680" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G680" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30156,7 +30800,11 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J680" s="7" t="inlineStr"/>
+      <c r="J680" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="7" t="n">
@@ -30180,7 +30828,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F681" s="8" t="inlineStr"/>
+      <c r="F681" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G681" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30196,11 +30848,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J681" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (23 colours)</t>
-        </is>
-      </c>
+      <c r="J681" s="7" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="7" t="n">
@@ -30224,7 +30872,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F682" s="8" t="inlineStr"/>
+      <c r="F682" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G682" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30240,11 +30892,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J682" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (18 colours)</t>
-        </is>
-      </c>
+      <c r="J682" s="7" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="7" t="n">
@@ -30530,7 +31178,7 @@
       </c>
       <c r="J688" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 70x86); shiny front: resize/redraw (96x96, art 70x86); shiny back: resize/redraw (18 colours)</t>
+          <t>front: resize/redraw (96x96, art 70x86); shiny front: resize/redraw (96x96, art 70x86)</t>
         </is>
       </c>
     </row>
@@ -30796,7 +31444,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F694" s="8" t="inlineStr"/>
+      <c r="F694" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G694" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30814,7 +31466,7 @@
       </c>
       <c r="J694" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 87x78)</t>
+          <t>front: resize/redraw (96x96, art 87x78); shiny front: resize/redraw (96x96, art 87x78)</t>
         </is>
       </c>
     </row>
@@ -30910,7 +31562,7 @@
       </c>
       <c r="J696" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (not a clean 2x upscale)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -31102,7 +31754,7 @@
       </c>
       <c r="J700" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 78x86); shiny front: resize/redraw (96x96, art 78x86); shiny back: resize/redraw (17 colours)</t>
+          <t>front: resize/redraw (96x96, art 78x86); back: resize/redraw (18 colours); shiny front: resize/redraw (96x96, art 78x86); shiny back: resize/redraw (18 colours)</t>
         </is>
       </c>
     </row>
@@ -31390,7 +32042,7 @@
       </c>
       <c r="J706" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (not a clean 2x upscale)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -31582,7 +32234,7 @@
       </c>
       <c r="J710" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 81x85); shiny front: resize/redraw (96x96, art 81x85); shiny back: resize/redraw (17 colours)</t>
+          <t>front: resize/redraw (96x96, art 81x85); shiny front: resize/redraw (96x96, art 81x85)</t>
         </is>
       </c>
     </row>
@@ -31608,8 +32260,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F711" s="8" t="inlineStr"/>
-      <c r="G711" s="8" t="inlineStr"/>
+      <c r="F711" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G711" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H711" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31644,8 +32304,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F712" s="8" t="inlineStr"/>
-      <c r="G712" s="8" t="inlineStr"/>
+      <c r="F712" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G712" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H712" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31733,7 +32401,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G714" s="8" t="inlineStr"/>
+      <c r="G714" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H714" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31794,7 +32466,7 @@
       </c>
       <c r="J715" s="7" t="inlineStr">
         <is>
-          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny back: resize/redraw (18 colours)</t>
+          <t>front: crop to 80x80 (96x96 canvas, art fits 80x80); shiny front: crop to 80x80 (96x96 canvas, art fits 80x80)</t>
         </is>
       </c>
     </row>
@@ -31842,7 +32514,7 @@
       </c>
       <c r="J716" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 96x75); shiny front: resize/redraw (96x96, art 96x75); shiny back: resize/redraw (38 colours)</t>
+          <t>front: resize/redraw (96x96, art 96x75); shiny front: resize/redraw (17 colours)</t>
         </is>
       </c>
     </row>
@@ -31868,7 +32540,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F717" s="8" t="inlineStr"/>
+      <c r="F717" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G717" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31884,11 +32560,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J717" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (34 colours)</t>
-        </is>
-      </c>
+      <c r="J717" s="7" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="7" t="n">
@@ -31934,7 +32606,7 @@
       </c>
       <c r="J718" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 93x96); shiny front: resize/redraw (96x96, art 93x96); shiny back: resize/redraw (30 colours)</t>
+          <t>front: resize/redraw (96x96, art 93x96); shiny front: resize/redraw (96x96, art 93x96)</t>
         </is>
       </c>
     </row>
@@ -31960,7 +32632,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F719" s="8" t="inlineStr"/>
+      <c r="F719" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G719" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -32000,7 +32676,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F720" s="8" t="inlineStr"/>
+      <c r="F720" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G720" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -32016,11 +32696,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J720" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (18 colours)</t>
-        </is>
-      </c>
+      <c r="J720" s="7" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="7" t="n">
@@ -32044,7 +32720,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F721" s="8" t="inlineStr"/>
+      <c r="F721" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G721" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -32060,11 +32740,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J721" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (25 colours)</t>
-        </is>
-      </c>
+      <c r="J721" s="7" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="7" t="n">
@@ -32110,7 +32786,7 @@
       </c>
       <c r="J722" s="7" t="inlineStr">
         <is>
-          <t>front: resize/redraw (96x96, art 77x85); shiny front: resize/redraw (96x96, art 77x85); shiny back: resize/redraw (24 colours)</t>
+          <t>front: resize/redraw (96x96, art 77x85); shiny front: resize/redraw (96x96, art 77x85)</t>
         </is>
       </c>
     </row>
@@ -33048,8 +33724,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F742" s="8" t="inlineStr"/>
-      <c r="G742" s="8" t="inlineStr"/>
+      <c r="F742" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G742" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H742" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -33228,7 +33912,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F746" s="8" t="inlineStr"/>
+      <c r="F746" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G746" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -33268,7 +33956,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F747" s="8" t="inlineStr"/>
+      <c r="F747" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G747" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -34556,7 +35248,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F774" s="8" t="inlineStr"/>
+      <c r="F774" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G774" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -34572,11 +35268,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J774" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (16 colours)</t>
-        </is>
-      </c>
+      <c r="J774" s="7" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" s="7" t="n">
@@ -34600,8 +35292,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F775" s="8" t="inlineStr"/>
-      <c r="G775" s="8" t="inlineStr"/>
+      <c r="F775" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G775" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H775" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -34780,7 +35480,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F779" s="8" t="inlineStr"/>
+      <c r="F779" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G779" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35396,8 +36100,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F792" s="8" t="inlineStr"/>
-      <c r="G792" s="8" t="inlineStr"/>
+      <c r="F792" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G792" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H792" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35432,8 +36144,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F793" s="8" t="inlineStr"/>
-      <c r="G793" s="8" t="inlineStr"/>
+      <c r="F793" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G793" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H793" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35804,8 +36524,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F801" s="8" t="inlineStr"/>
-      <c r="G801" s="8" t="inlineStr"/>
+      <c r="F801" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G801" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H801" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35840,8 +36568,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F802" s="8" t="inlineStr"/>
-      <c r="G802" s="8" t="inlineStr"/>
+      <c r="F802" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G802" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H802" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35852,7 +36588,11 @@
           <t>Gen5-9 Sprites part 1; PokeAPI Gen VII (USUM) icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J802" s="7" t="inlineStr"/>
+      <c r="J802" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (18 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="7" t="n">
@@ -35876,7 +36616,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F803" s="8" t="inlineStr"/>
+      <c r="F803" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G803" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36204,8 +36948,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F810" s="8" t="inlineStr"/>
-      <c r="G810" s="8" t="inlineStr"/>
+      <c r="F810" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G810" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H810" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36336,7 +37088,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F813" s="8" t="inlineStr"/>
+      <c r="F813" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G813" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36352,11 +37108,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J813" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (17 colours)</t>
-        </is>
-      </c>
+      <c r="J813" s="7" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" s="7" t="n">
@@ -36476,7 +37228,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F816" s="8" t="inlineStr"/>
+      <c r="F816" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G816" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36612,7 +37368,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F819" s="8" t="inlineStr"/>
+      <c r="F819" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G819" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36628,7 +37388,11 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J819" s="7" t="inlineStr"/>
+      <c r="J819" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="7" t="n">
@@ -36844,7 +37608,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F824" s="8" t="inlineStr"/>
+      <c r="F824" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G824" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36980,7 +37748,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F827" s="8" t="inlineStr"/>
+      <c r="F827" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G827" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -36998,7 +37770,7 @@
       </c>
       <c r="J827" s="7" t="inlineStr">
         <is>
-          <t>shiny back: resize/redraw (36 colours)</t>
+          <t>shiny front: resize/redraw (17 colours)</t>
         </is>
       </c>
     </row>
@@ -37360,8 +38132,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F835" s="8" t="inlineStr"/>
-      <c r="G835" s="8" t="inlineStr"/>
+      <c r="F835" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G835" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H835" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -37372,7 +38152,11 @@
           <t>Gen5-9 Sprites part 1; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J835" s="7" t="inlineStr"/>
+      <c r="J835" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="7" t="n">
@@ -37588,7 +38372,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F840" s="8" t="inlineStr"/>
+      <c r="F840" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G840" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -37676,7 +38464,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F842" s="8" t="inlineStr"/>
+      <c r="F842" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G842" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -37692,11 +38484,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J842" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (19 colours)</t>
-        </is>
-      </c>
+      <c r="J842" s="7" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" s="7" t="n">
@@ -37720,7 +38508,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F843" s="8" t="inlineStr"/>
+      <c r="F843" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G843" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -37808,8 +38600,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F845" s="8" t="inlineStr"/>
-      <c r="G845" s="8" t="inlineStr"/>
+      <c r="F845" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G845" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H845" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -37844,8 +38644,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F846" s="8" t="inlineStr"/>
-      <c r="G846" s="8" t="inlineStr"/>
+      <c r="F846" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G846" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H846" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38024,8 +38832,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F850" s="8" t="inlineStr"/>
-      <c r="G850" s="8" t="inlineStr"/>
+      <c r="F850" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G850" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H850" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38108,7 +38924,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F852" s="8" t="inlineStr"/>
+      <c r="F852" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G852" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38436,7 +39256,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F859" s="8" t="inlineStr"/>
+      <c r="F859" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G859" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38452,11 +39276,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J859" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (not a clean 2x upscale)</t>
-        </is>
-      </c>
+      <c r="J859" s="7" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" s="7" t="n">
@@ -38576,7 +39396,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F862" s="8" t="inlineStr"/>
+      <c r="F862" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G862" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38952,7 +39776,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F870" s="8" t="inlineStr"/>
+      <c r="F870" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G870" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -38968,11 +39796,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J870" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (not a clean 2x upscale)</t>
-        </is>
-      </c>
+      <c r="J870" s="7" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" s="7" t="n">
@@ -39236,7 +40060,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F876" s="8" t="inlineStr"/>
+      <c r="F876" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G876" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39324,8 +40152,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F878" s="8" t="inlineStr"/>
-      <c r="G878" s="8" t="inlineStr"/>
+      <c r="F878" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G878" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H878" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39408,7 +40244,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F880" s="8" t="inlineStr"/>
+      <c r="F880" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G880" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39640,8 +40480,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F885" s="8" t="inlineStr"/>
-      <c r="G885" s="8" t="inlineStr"/>
+      <c r="F885" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G885" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H885" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39820,8 +40668,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F889" s="8" t="inlineStr"/>
-      <c r="G889" s="8" t="inlineStr"/>
+      <c r="F889" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G889" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H889" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39856,8 +40712,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F890" s="8" t="inlineStr"/>
-      <c r="G890" s="8" t="inlineStr"/>
+      <c r="F890" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G890" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H890" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39892,7 +40756,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F891" s="8" t="inlineStr"/>
+      <c r="F891" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G891" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39980,7 +40848,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F893" s="8" t="inlineStr"/>
+      <c r="F893" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G893" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -39996,11 +40868,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J893" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (19 colours)</t>
-        </is>
-      </c>
+      <c r="J893" s="7" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" s="7" t="n">
@@ -40024,7 +40892,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F894" s="8" t="inlineStr"/>
+      <c r="F894" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G894" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40040,7 +40912,11 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Sword/Shield icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J894" s="7" t="inlineStr"/>
+      <c r="J894" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" s="7" t="n">
@@ -40256,8 +41132,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F899" s="8" t="inlineStr"/>
-      <c r="G899" s="8" t="inlineStr"/>
+      <c r="F899" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G899" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H899" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40292,8 +41176,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F900" s="8" t="inlineStr"/>
-      <c r="G900" s="8" t="inlineStr"/>
+      <c r="F900" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G900" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H900" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40328,7 +41220,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F901" s="8" t="inlineStr"/>
+      <c r="F901" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G901" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40368,7 +41264,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F902" s="8" t="inlineStr"/>
+      <c r="F902" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G902" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40384,7 +41284,11 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J902" s="7" t="inlineStr"/>
+      <c r="J902" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (17 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" s="7" t="n">
@@ -40408,7 +41312,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F903" s="8" t="inlineStr"/>
+      <c r="F903" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G903" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40424,11 +41332,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J903" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (16 colours)</t>
-        </is>
-      </c>
+      <c r="J903" s="7" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" s="7" t="n">
@@ -40452,7 +41356,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F904" s="8" t="inlineStr"/>
+      <c r="F904" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G904" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40468,11 +41376,7 @@
           <t>Gen5-9 Sprites part 1; DPPt Style Gen VI and Beyond; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J904" s="7" t="inlineStr">
-        <is>
-          <t>shiny back: resize/redraw (17 colours)</t>
-        </is>
-      </c>
+      <c r="J904" s="7" t="inlineStr"/>
     </row>
     <row r="905">
       <c r="A905" s="7" t="n">
@@ -40496,7 +41400,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F905" s="8" t="inlineStr"/>
+      <c r="F905" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G905" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40536,8 +41444,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F906" s="8" t="inlineStr"/>
-      <c r="G906" s="8" t="inlineStr"/>
+      <c r="F906" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G906" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H906" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40572,8 +41488,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F907" s="8" t="inlineStr"/>
-      <c r="G907" s="8" t="inlineStr"/>
+      <c r="F907" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G907" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H907" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40608,8 +41532,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F908" s="8" t="inlineStr"/>
-      <c r="G908" s="8" t="inlineStr"/>
+      <c r="F908" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G908" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H908" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40644,8 +41576,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F909" s="8" t="inlineStr"/>
-      <c r="G909" s="8" t="inlineStr"/>
+      <c r="F909" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G909" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H909" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40680,8 +41620,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F910" s="8" t="inlineStr"/>
-      <c r="G910" s="8" t="inlineStr"/>
+      <c r="F910" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G910" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H910" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40716,8 +41664,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F911" s="8" t="inlineStr"/>
-      <c r="G911" s="8" t="inlineStr"/>
+      <c r="F911" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G911" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H911" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40752,8 +41708,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F912" s="8" t="inlineStr"/>
-      <c r="G912" s="8" t="inlineStr"/>
+      <c r="F912" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G912" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H912" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40788,8 +41752,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F913" s="8" t="inlineStr"/>
-      <c r="G913" s="8" t="inlineStr"/>
+      <c r="F913" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G913" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H913" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40824,8 +41796,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F914" s="8" t="inlineStr"/>
-      <c r="G914" s="8" t="inlineStr"/>
+      <c r="F914" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G914" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H914" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40860,8 +41840,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F915" s="8" t="inlineStr"/>
-      <c r="G915" s="8" t="inlineStr"/>
+      <c r="F915" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G915" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H915" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40896,8 +41884,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F916" s="8" t="inlineStr"/>
-      <c r="G916" s="8" t="inlineStr"/>
+      <c r="F916" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G916" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H916" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40932,8 +41928,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F917" s="8" t="inlineStr"/>
-      <c r="G917" s="8" t="inlineStr"/>
+      <c r="F917" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G917" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H917" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -40968,8 +41972,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F918" s="8" t="inlineStr"/>
-      <c r="G918" s="8" t="inlineStr"/>
+      <c r="F918" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G918" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H918" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41004,8 +42016,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F919" s="8" t="inlineStr"/>
-      <c r="G919" s="8" t="inlineStr"/>
+      <c r="F919" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G919" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H919" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41016,7 +42036,11 @@
           <t>Gen5-9 Sprites part 1; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J919" s="7" t="inlineStr"/>
+      <c r="J919" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="7" t="n">
@@ -41040,8 +42064,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F920" s="8" t="inlineStr"/>
-      <c r="G920" s="8" t="inlineStr"/>
+      <c r="F920" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G920" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H920" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41076,8 +42108,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F921" s="8" t="inlineStr"/>
-      <c r="G921" s="8" t="inlineStr"/>
+      <c r="F921" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G921" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H921" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41112,8 +42152,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F922" s="8" t="inlineStr"/>
-      <c r="G922" s="8" t="inlineStr"/>
+      <c r="F922" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G922" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H922" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41148,8 +42196,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F923" s="8" t="inlineStr"/>
-      <c r="G923" s="8" t="inlineStr"/>
+      <c r="F923" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G923" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H923" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41184,8 +42240,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F924" s="8" t="inlineStr"/>
-      <c r="G924" s="8" t="inlineStr"/>
+      <c r="F924" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G924" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H924" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41220,8 +42284,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F925" s="8" t="inlineStr"/>
-      <c r="G925" s="8" t="inlineStr"/>
+      <c r="F925" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G925" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H925" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41256,8 +42328,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F926" s="8" t="inlineStr"/>
-      <c r="G926" s="8" t="inlineStr"/>
+      <c r="F926" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G926" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H926" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41292,8 +42372,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F927" s="8" t="inlineStr"/>
-      <c r="G927" s="8" t="inlineStr"/>
+      <c r="F927" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G927" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H927" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41328,8 +42416,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F928" s="8" t="inlineStr"/>
-      <c r="G928" s="8" t="inlineStr"/>
+      <c r="F928" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G928" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H928" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41364,8 +42460,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F929" s="8" t="inlineStr"/>
-      <c r="G929" s="8" t="inlineStr"/>
+      <c r="F929" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G929" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H929" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41400,8 +42504,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F930" s="8" t="inlineStr"/>
-      <c r="G930" s="8" t="inlineStr"/>
+      <c r="F930" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G930" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H930" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41436,8 +42548,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F931" s="8" t="inlineStr"/>
-      <c r="G931" s="8" t="inlineStr"/>
+      <c r="F931" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G931" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H931" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41472,8 +42592,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F932" s="8" t="inlineStr"/>
-      <c r="G932" s="8" t="inlineStr"/>
+      <c r="F932" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G932" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H932" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41508,8 +42636,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F933" s="8" t="inlineStr"/>
-      <c r="G933" s="8" t="inlineStr"/>
+      <c r="F933" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G933" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H933" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41544,8 +42680,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F934" s="8" t="inlineStr"/>
-      <c r="G934" s="8" t="inlineStr"/>
+      <c r="F934" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G934" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H934" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41580,8 +42724,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F935" s="8" t="inlineStr"/>
-      <c r="G935" s="8" t="inlineStr"/>
+      <c r="F935" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G935" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H935" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41616,8 +42768,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F936" s="8" t="inlineStr"/>
-      <c r="G936" s="8" t="inlineStr"/>
+      <c r="F936" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G936" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H936" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41652,8 +42812,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F937" s="8" t="inlineStr"/>
-      <c r="G937" s="8" t="inlineStr"/>
+      <c r="F937" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G937" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H937" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41688,8 +42856,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F938" s="8" t="inlineStr"/>
-      <c r="G938" s="8" t="inlineStr"/>
+      <c r="F938" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G938" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H938" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41700,7 +42876,11 @@
           <t>Gen5-9 Sprites part 1; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J938" s="7" t="inlineStr"/>
+      <c r="J938" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (16 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="7" t="n">
@@ -41724,8 +42904,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F939" s="8" t="inlineStr"/>
-      <c r="G939" s="8" t="inlineStr"/>
+      <c r="F939" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G939" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H939" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41760,8 +42948,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F940" s="8" t="inlineStr"/>
-      <c r="G940" s="8" t="inlineStr"/>
+      <c r="F940" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G940" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H940" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41796,8 +42992,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F941" s="8" t="inlineStr"/>
-      <c r="G941" s="8" t="inlineStr"/>
+      <c r="F941" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G941" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H941" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41832,8 +43036,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F942" s="8" t="inlineStr"/>
-      <c r="G942" s="8" t="inlineStr"/>
+      <c r="F942" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G942" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H942" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41868,8 +43080,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F943" s="8" t="inlineStr"/>
-      <c r="G943" s="8" t="inlineStr"/>
+      <c r="F943" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G943" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H943" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41904,8 +43124,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F944" s="8" t="inlineStr"/>
-      <c r="G944" s="8" t="inlineStr"/>
+      <c r="F944" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G944" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H944" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41940,8 +43168,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F945" s="8" t="inlineStr"/>
-      <c r="G945" s="8" t="inlineStr"/>
+      <c r="F945" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G945" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H945" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41976,8 +43212,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F946" s="8" t="inlineStr"/>
-      <c r="G946" s="8" t="inlineStr"/>
+      <c r="F946" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G946" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H946" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42012,8 +43256,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F947" s="8" t="inlineStr"/>
-      <c r="G947" s="8" t="inlineStr"/>
+      <c r="F947" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G947" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H947" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42048,8 +43300,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F948" s="8" t="inlineStr"/>
-      <c r="G948" s="8" t="inlineStr"/>
+      <c r="F948" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G948" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H948" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42084,8 +43344,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F949" s="8" t="inlineStr"/>
-      <c r="G949" s="8" t="inlineStr"/>
+      <c r="F949" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G949" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H949" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42120,8 +43388,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F950" s="8" t="inlineStr"/>
-      <c r="G950" s="8" t="inlineStr"/>
+      <c r="F950" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G950" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H950" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42156,8 +43432,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F951" s="8" t="inlineStr"/>
-      <c r="G951" s="8" t="inlineStr"/>
+      <c r="F951" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G951" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H951" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42192,8 +43476,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F952" s="8" t="inlineStr"/>
-      <c r="G952" s="8" t="inlineStr"/>
+      <c r="F952" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G952" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H952" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42228,8 +43520,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F953" s="8" t="inlineStr"/>
-      <c r="G953" s="8" t="inlineStr"/>
+      <c r="F953" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G953" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H953" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42264,8 +43564,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F954" s="8" t="inlineStr"/>
-      <c r="G954" s="8" t="inlineStr"/>
+      <c r="F954" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G954" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H954" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42300,8 +43608,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F955" s="8" t="inlineStr"/>
-      <c r="G955" s="8" t="inlineStr"/>
+      <c r="F955" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G955" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H955" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42336,8 +43652,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F956" s="8" t="inlineStr"/>
-      <c r="G956" s="8" t="inlineStr"/>
+      <c r="F956" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G956" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H956" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42372,8 +43696,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F957" s="8" t="inlineStr"/>
-      <c r="G957" s="8" t="inlineStr"/>
+      <c r="F957" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G957" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H957" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42384,7 +43716,11 @@
           <t>Gen5-9 Sprites part 1; PokeAPI Scarlet/Violet icon (placeholder icon)</t>
         </is>
       </c>
-      <c r="J957" s="7" t="inlineStr"/>
+      <c r="J957" s="7" t="inlineStr">
+        <is>
+          <t>shiny front: resize/redraw (18 colours)</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="7" t="n">
@@ -42408,8 +43744,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F958" s="8" t="inlineStr"/>
-      <c r="G958" s="8" t="inlineStr"/>
+      <c r="F958" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G958" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H958" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42444,8 +43788,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F959" s="8" t="inlineStr"/>
-      <c r="G959" s="8" t="inlineStr"/>
+      <c r="F959" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G959" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H959" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42480,8 +43832,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F960" s="8" t="inlineStr"/>
-      <c r="G960" s="8" t="inlineStr"/>
+      <c r="F960" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G960" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H960" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42516,8 +43876,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F961" s="8" t="inlineStr"/>
-      <c r="G961" s="8" t="inlineStr"/>
+      <c r="F961" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G961" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H961" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42552,8 +43920,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F962" s="8" t="inlineStr"/>
-      <c r="G962" s="8" t="inlineStr"/>
+      <c r="F962" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G962" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H962" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42588,8 +43964,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F963" s="8" t="inlineStr"/>
-      <c r="G963" s="8" t="inlineStr"/>
+      <c r="F963" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G963" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H963" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42624,8 +44008,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F964" s="8" t="inlineStr"/>
-      <c r="G964" s="8" t="inlineStr"/>
+      <c r="F964" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G964" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H964" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42660,8 +44052,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F965" s="8" t="inlineStr"/>
-      <c r="G965" s="8" t="inlineStr"/>
+      <c r="F965" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G965" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H965" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42696,8 +44096,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F966" s="8" t="inlineStr"/>
-      <c r="G966" s="8" t="inlineStr"/>
+      <c r="F966" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G966" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H966" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42732,8 +44140,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F967" s="8" t="inlineStr"/>
-      <c r="G967" s="8" t="inlineStr"/>
+      <c r="F967" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G967" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H967" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42768,8 +44184,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F968" s="8" t="inlineStr"/>
-      <c r="G968" s="8" t="inlineStr"/>
+      <c r="F968" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G968" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H968" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42804,8 +44228,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F969" s="8" t="inlineStr"/>
-      <c r="G969" s="8" t="inlineStr"/>
+      <c r="F969" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G969" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H969" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42840,8 +44272,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F970" s="8" t="inlineStr"/>
-      <c r="G970" s="8" t="inlineStr"/>
+      <c r="F970" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G970" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H970" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42876,8 +44316,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F971" s="8" t="inlineStr"/>
-      <c r="G971" s="8" t="inlineStr"/>
+      <c r="F971" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G971" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H971" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42912,8 +44360,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F972" s="8" t="inlineStr"/>
-      <c r="G972" s="8" t="inlineStr"/>
+      <c r="F972" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G972" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H972" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42948,8 +44404,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F973" s="8" t="inlineStr"/>
-      <c r="G973" s="8" t="inlineStr"/>
+      <c r="F973" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G973" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H973" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42984,8 +44448,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F974" s="8" t="inlineStr"/>
-      <c r="G974" s="8" t="inlineStr"/>
+      <c r="F974" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G974" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H974" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43020,8 +44492,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F975" s="8" t="inlineStr"/>
-      <c r="G975" s="8" t="inlineStr"/>
+      <c r="F975" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G975" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H975" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43056,8 +44536,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F976" s="8" t="inlineStr"/>
-      <c r="G976" s="8" t="inlineStr"/>
+      <c r="F976" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G976" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H976" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43092,8 +44580,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F977" s="8" t="inlineStr"/>
-      <c r="G977" s="8" t="inlineStr"/>
+      <c r="F977" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G977" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H977" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43128,8 +44624,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F978" s="8" t="inlineStr"/>
-      <c r="G978" s="8" t="inlineStr"/>
+      <c r="F978" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G978" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H978" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43164,8 +44668,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F979" s="8" t="inlineStr"/>
-      <c r="G979" s="8" t="inlineStr"/>
+      <c r="F979" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G979" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H979" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43200,8 +44712,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F980" s="8" t="inlineStr"/>
-      <c r="G980" s="8" t="inlineStr"/>
+      <c r="F980" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G980" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H980" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43236,8 +44756,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F981" s="8" t="inlineStr"/>
-      <c r="G981" s="8" t="inlineStr"/>
+      <c r="F981" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G981" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H981" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43272,8 +44800,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F982" s="8" t="inlineStr"/>
-      <c r="G982" s="8" t="inlineStr"/>
+      <c r="F982" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G982" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H982" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43308,8 +44844,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F983" s="8" t="inlineStr"/>
-      <c r="G983" s="8" t="inlineStr"/>
+      <c r="F983" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G983" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H983" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43344,8 +44888,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F984" s="8" t="inlineStr"/>
-      <c r="G984" s="8" t="inlineStr"/>
+      <c r="F984" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G984" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H984" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43380,8 +44932,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F985" s="8" t="inlineStr"/>
-      <c r="G985" s="8" t="inlineStr"/>
+      <c r="F985" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G985" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H985" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43416,8 +44976,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F986" s="8" t="inlineStr"/>
-      <c r="G986" s="8" t="inlineStr"/>
+      <c r="F986" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G986" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H986" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43452,8 +45020,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F987" s="8" t="inlineStr"/>
-      <c r="G987" s="8" t="inlineStr"/>
+      <c r="F987" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G987" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H987" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43488,8 +45064,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F988" s="8" t="inlineStr"/>
-      <c r="G988" s="8" t="inlineStr"/>
+      <c r="F988" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G988" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H988" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43524,8 +45108,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F989" s="8" t="inlineStr"/>
-      <c r="G989" s="8" t="inlineStr"/>
+      <c r="F989" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G989" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H989" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43560,8 +45152,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F990" s="8" t="inlineStr"/>
-      <c r="G990" s="8" t="inlineStr"/>
+      <c r="F990" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G990" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H990" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43596,8 +45196,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F991" s="8" t="inlineStr"/>
-      <c r="G991" s="8" t="inlineStr"/>
+      <c r="F991" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G991" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H991" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43632,8 +45240,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F992" s="8" t="inlineStr"/>
-      <c r="G992" s="8" t="inlineStr"/>
+      <c r="F992" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G992" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H992" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43668,8 +45284,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F993" s="8" t="inlineStr"/>
-      <c r="G993" s="8" t="inlineStr"/>
+      <c r="F993" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G993" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H993" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43704,8 +45328,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F994" s="8" t="inlineStr"/>
-      <c r="G994" s="8" t="inlineStr"/>
+      <c r="F994" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G994" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H994" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43740,8 +45372,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F995" s="8" t="inlineStr"/>
-      <c r="G995" s="8" t="inlineStr"/>
+      <c r="F995" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G995" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H995" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43776,8 +45416,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F996" s="8" t="inlineStr"/>
-      <c r="G996" s="8" t="inlineStr"/>
+      <c r="F996" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G996" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H996" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43812,8 +45460,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F997" s="8" t="inlineStr"/>
-      <c r="G997" s="8" t="inlineStr"/>
+      <c r="F997" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G997" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H997" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43848,8 +45504,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F998" s="8" t="inlineStr"/>
-      <c r="G998" s="8" t="inlineStr"/>
+      <c r="F998" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G998" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H998" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43884,8 +45548,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F999" s="8" t="inlineStr"/>
-      <c r="G999" s="8" t="inlineStr"/>
+      <c r="F999" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G999" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H999" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43920,8 +45592,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1000" s="8" t="inlineStr"/>
-      <c r="G1000" s="8" t="inlineStr"/>
+      <c r="F1000" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1000" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1000" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43956,8 +45636,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1001" s="8" t="inlineStr"/>
-      <c r="G1001" s="8" t="inlineStr"/>
+      <c r="F1001" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1001" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1001" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43992,8 +45680,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1002" s="8" t="inlineStr"/>
-      <c r="G1002" s="8" t="inlineStr"/>
+      <c r="F1002" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1002" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1002" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44028,8 +45724,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1003" s="8" t="inlineStr"/>
-      <c r="G1003" s="8" t="inlineStr"/>
+      <c r="F1003" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1003" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1003" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44064,8 +45768,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1004" s="8" t="inlineStr"/>
-      <c r="G1004" s="8" t="inlineStr"/>
+      <c r="F1004" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1004" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1004" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44100,8 +45812,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1005" s="8" t="inlineStr"/>
-      <c r="G1005" s="8" t="inlineStr"/>
+      <c r="F1005" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1005" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1005" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44136,8 +45856,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1006" s="8" t="inlineStr"/>
-      <c r="G1006" s="8" t="inlineStr"/>
+      <c r="F1006" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1006" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1006" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44172,8 +45900,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1007" s="8" t="inlineStr"/>
-      <c r="G1007" s="8" t="inlineStr"/>
+      <c r="F1007" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1007" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1007" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44208,8 +45944,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1008" s="8" t="inlineStr"/>
-      <c r="G1008" s="8" t="inlineStr"/>
+      <c r="F1008" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1008" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1008" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44244,8 +45988,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1009" s="8" t="inlineStr"/>
-      <c r="G1009" s="8" t="inlineStr"/>
+      <c r="F1009" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1009" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1009" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44280,8 +46032,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1010" s="8" t="inlineStr"/>
-      <c r="G1010" s="8" t="inlineStr"/>
+      <c r="F1010" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1010" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1010" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44316,8 +46076,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1011" s="8" t="inlineStr"/>
-      <c r="G1011" s="8" t="inlineStr"/>
+      <c r="F1011" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1011" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1011" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44352,8 +46120,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1012" s="8" t="inlineStr"/>
-      <c r="G1012" s="8" t="inlineStr"/>
+      <c r="F1012" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1012" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1012" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44388,8 +46164,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1013" s="8" t="inlineStr"/>
-      <c r="G1013" s="8" t="inlineStr"/>
+      <c r="F1013" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1013" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1013" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44424,8 +46208,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1014" s="8" t="inlineStr"/>
-      <c r="G1014" s="8" t="inlineStr"/>
+      <c r="F1014" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1014" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1014" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44460,8 +46252,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1015" s="8" t="inlineStr"/>
-      <c r="G1015" s="8" t="inlineStr"/>
+      <c r="F1015" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1015" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1015" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44496,8 +46296,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1016" s="8" t="inlineStr"/>
-      <c r="G1016" s="8" t="inlineStr"/>
+      <c r="F1016" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1016" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1016" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44532,8 +46340,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1017" s="8" t="inlineStr"/>
-      <c r="G1017" s="8" t="inlineStr"/>
+      <c r="F1017" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1017" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1017" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44568,8 +46384,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1018" s="8" t="inlineStr"/>
-      <c r="G1018" s="8" t="inlineStr"/>
+      <c r="F1018" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1018" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1018" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44604,8 +46428,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1019" s="8" t="inlineStr"/>
-      <c r="G1019" s="8" t="inlineStr"/>
+      <c r="F1019" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1019" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1019" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44640,8 +46472,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1020" s="8" t="inlineStr"/>
-      <c r="G1020" s="8" t="inlineStr"/>
+      <c r="F1020" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1020" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1020" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44676,8 +46516,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1021" s="8" t="inlineStr"/>
-      <c r="G1021" s="8" t="inlineStr"/>
+      <c r="F1021" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1021" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1021" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44712,8 +46560,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1022" s="8" t="inlineStr"/>
-      <c r="G1022" s="8" t="inlineStr"/>
+      <c r="F1022" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1022" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1022" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44748,8 +46604,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1023" s="8" t="inlineStr"/>
-      <c r="G1023" s="8" t="inlineStr"/>
+      <c r="F1023" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1023" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1023" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44784,8 +46648,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1024" s="8" t="inlineStr"/>
-      <c r="G1024" s="8" t="inlineStr"/>
+      <c r="F1024" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1024" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1024" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44820,8 +46692,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1025" s="8" t="inlineStr"/>
-      <c r="G1025" s="8" t="inlineStr"/>
+      <c r="F1025" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1025" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1025" s="5" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44856,8 +46736,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F1026" s="8" t="inlineStr"/>
-      <c r="G1026" s="8" t="inlineStr"/>
+      <c r="F1026" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G1026" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H1026" s="5" t="inlineStr">
         <is>
           <t>✓</t>
